--- a/docs/DDR4_PinDescription.xlsx
+++ b/docs/DDR4_PinDescription.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PCB\Project\DDR4_DIMM_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A36286E-183F-4882-84E2-2168EFDD5DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4F0254-5819-4D06-A603-64D1B74105DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{5EF2FE71-DCD4-4236-92FA-B5935CC9F8C6}"/>
   </bookViews>
